--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R452e5c6d523b43c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R7f308dd26ef541a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1344,7 +1344,7 @@
       </x:c>
       <x:c r="D16" s="32" t="str">
         <x:v>아래 템플릿 저장소를 엽니다.
-참고  https://github.com/jyejye-school/training-sign-template</x:v>
+참고  https://github.com/school-training-sign/training-sign-template</x:v>
       </x:c>
       <x:c r="E16" s="109"/>
       <x:c r="F16" s="3"/>

--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R22398b158c734fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R20213cef86c242cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1488,7 +1488,7 @@
       </x:c>
       <x:c r="D26" s="32" t="str">
         <x:v>연수에서 날짜·시간·활성 상태와 서명 대상(전체 구성원 또는 부서 선택)을 정합니다.
-참고  선택한 부서에 나중에 추가되는 구성원도 자동으로 대상에 포함됩니다. 지난 연수도 활성화하면 재수합할 수 있습니다.</x:v>
+참고  필요한 연수에만 현장 접수 코드 사용을 켭니다. 기존 연수와 이 항목을 끈 연수는 코드 없이 운영됩니다.</x:v>
       </x:c>
       <x:c r="E26" s="109"/>
       <x:c r="F26" s="3"/>
@@ -1538,11 +1538,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="66" t="str">
-        <x:v>참여 화면 점검</x:v>
+        <x:v>현장 접수와 참여</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>연수 날짜·시간·활성 상태를 확인하고 공유 링크를 휴대폰에서도 열어 봅니다.
-참고  참여자는 연수 선택 → 본인 선택 → 서명 제출 순서로 진행합니다.</x:v>
+        <x:v>현장 코드 연수는 카드에서 5·10·15분 접수를 열고 화면의 6자리 코드를 현장에서 안내합니다.
+참고  재발급·종료 시 이전 코드는 즉시 무효화되며, 오늘·매일 연수는 등록된 종료 시각에 맞춰 접수도 끝납니다.</x:v>
       </x:c>
       <x:c r="E30" s="109"/>
       <x:c r="F30" s="3"/>

--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R20213cef86c242cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="Rfea43fbf87014609"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="13">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -86,8 +86,30 @@
       <x:color rgb="FF34425E"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF14213D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF64748B"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -177,6 +199,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF165DFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF18794E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF7F0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6F42C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3EDFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F8FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFB42318"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -512,7 +594,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="136">
+  <x:cellXfs count="238">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -913,6 +995,308 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="22" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="27" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="27" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="28" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="30" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="30" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1191,575 +1575,476 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="3"/>
-      <x:c r="B6" s="106" t="str">
-        <x:v>1. 학교용 사본과 Google 백엔드 만들기</x:v>
-      </x:c>
-      <x:c r="C6" s="23" t="str">
-        <x:v>1. 학교용 사본과 Google 백엔드 만들기</x:v>
-      </x:c>
-      <x:c r="D6" s="23" t="str">
-        <x:v>1. 학교용 사본과 Google 백엔드 만들기</x:v>
-      </x:c>
-      <x:c r="E6" s="107" t="str">
-        <x:v>1. 학교용 사본과 Google 백엔드 만들기</x:v>
-      </x:c>
+      <x:c r="B6" s="147" t="str">
+        <x:v>1. 학교용 사본과 웹앱 만들기</x:v>
+      </x:c>
+      <x:c r="C6" s="148"/>
+      <x:c r="D6" s="148"/>
+      <x:c r="E6" s="149"/>
       <x:c r="F6" s="3"/>
     </x:row>
     <x:row r="7" ht="43.5" customHeight="1">
       <x:c r="A7" s="3"/>
-      <x:c r="B7" s="108" t="str">
+      <x:c r="B7" s="152" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="31" t="str">
+      <x:c r="C7" s="156" t="str">
         <x:v>학교용 사본 만들기</x:v>
       </x:c>
-      <x:c r="D7" s="32" t="str">
+      <x:c r="D7" s="160" t="str">
         <x:v>상단 메뉴에서 파일 → 사본 만들기를 누릅니다.
-참고  사본 이름은 학교명이 드러나지 않는 관리용 이름으로 정해도 됩니다.</x:v>
-      </x:c>
-      <x:c r="E7" s="109"/>
+참고  반드시 새로 만든 사본에서 다음 단계를 진행합니다.</x:v>
+      </x:c>
+      <x:c r="E7" s="161"/>
       <x:c r="F7" s="3"/>
     </x:row>
-    <x:row r="8" ht="43.5" customHeight="1">
+    <x:row r="8" ht="100" customHeight="1">
       <x:c r="A8" s="3"/>
-      <x:c r="B8" s="108" t="str">
+      <x:c r="B8" s="152" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="31" t="str">
-        <x:v>초기 설정 실행</x:v>
-      </x:c>
-      <x:c r="D8" s="32" t="str">
-        <x:v>새 사본에서 🖊️ 전자서명 관리 → 초기 설정 실행을 누르고 Drive·Sheets 권한을 승인합니다.
-참고  설정·구성원·연수·서명·출력 작업·감사 기록 탭과 비공개 폴더가 자동으로 만들어집니다.</x:v>
-      </x:c>
-      <x:c r="E8" s="109"/>
+      <x:c r="C8" s="156" t="str">
+        <x:v>초기 설정과 권한 승인</x:v>
+      </x:c>
+      <x:c r="D8" s="160" t="str">
+        <x:v>새 사본에서 🖊️ 전자서명 관리 → 초기 설정 실행을 누르고, 완료 창의 초기 설정 코드를 보관합니다.
+참고  ‘Google에서 확인하지 않은 앱’이 나오면 개발자 이메일이 본인 계정인지 확인한 뒤 고급 → 학교 연수 전자서명 시스템으로 이동 → 허용을 누릅니다. 모르는 이메일이거나 Google Workspace 정책이 차단하면 중단하고 관리자에게 문의하세요. 소유자만 처음 한 번 승인하며 서명 참여자에게는 이 화면이 나타나지 않습니다.</x:v>
+      </x:c>
+      <x:c r="E8" s="161"/>
       <x:c r="F8" s="3"/>
     </x:row>
-    <x:row r="9" ht="43.5" customHeight="1">
+    <x:row r="9" ht="57" customHeight="1">
       <x:c r="A9" s="3"/>
-      <x:c r="B9" s="108" t="str">
+      <x:c r="B9" s="152" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
-        <x:v>초기 설정 코드 보관</x:v>
-      </x:c>
-      <x:c r="D9" s="32" t="str">
-        <x:v>완료 창에 나온 초기 설정 코드를 잠시 적어 둡니다.
-참고  첫 관리자 비밀번호를 만들면 자동으로 폐기됩니다.</x:v>
-      </x:c>
-      <x:c r="E9" s="109"/>
+      <x:c r="C9" s="156" t="str">
+        <x:v>웹앱 배포와 주소 복사</x:v>
+      </x:c>
+      <x:c r="D9" s="160" t="str">
+        <x:v>확장 프로그램 → Apps Script에서 배포 → 새 배포 → 유형 선택 → 웹 앱을 고릅니다.
+참고  실행 계정은 나, 액세스 권한은 모든 사용자로 설정해 배포한 뒤 /exec로 끝나는 웹 앱 URL을 복사합니다.</x:v>
+      </x:c>
+      <x:c r="E9" s="161"/>
       <x:c r="F9" s="3"/>
     </x:row>
-    <x:row r="10" ht="43.5" customHeight="1">
+    <x:row r="10" ht="20.25" customHeight="1">
       <x:c r="A10" s="3"/>
-      <x:c r="B10" s="108" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="31" t="str">
-        <x:v>Apps Script 열기</x:v>
-      </x:c>
-      <x:c r="D10" s="32" t="str">
-        <x:v>확장 프로그램 → Apps Script를 누릅니다.
-참고  연결된 스크립트가 새 학교용 사본과 함께 복사되어 있습니다.</x:v>
-      </x:c>
-      <x:c r="E10" s="109"/>
+      <x:c r="B10" s="138"/>
+      <x:c r="C10" s="138"/>
+      <x:c r="D10" s="138"/>
+      <x:c r="E10" s="138"/>
       <x:c r="F10" s="3"/>
     </x:row>
-    <x:row r="11" ht="43.5" customHeight="1">
+    <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="3"/>
-      <x:c r="B11" s="108" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="31" t="str">
-        <x:v>새 웹앱 배포</x:v>
-      </x:c>
-      <x:c r="D11" s="32" t="str">
-        <x:v>Apps Script 오른쪽 위 배포 → 새 배포 → 유형 선택 → 웹 앱을 고릅니다.
-참고  실행 계정은 나, 액세스 권한은 모든 사용자로 설정합니다.</x:v>
-      </x:c>
-      <x:c r="E11" s="109"/>
+      <x:c r="B11" s="170" t="str">
+        <x:v>2. 학교별 전자서명 화면 연결하기</x:v>
+      </x:c>
+      <x:c r="C11" s="171"/>
+      <x:c r="D11" s="171"/>
+      <x:c r="E11" s="172"/>
       <x:c r="F11" s="3"/>
     </x:row>
-    <x:row r="12" ht="43.5" customHeight="1">
+    <x:row r="12" ht="57" customHeight="1">
       <x:c r="A12" s="3"/>
-      <x:c r="B12" s="108" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="31" t="str">
-        <x:v>권한 승인</x:v>
-      </x:c>
-      <x:c r="D12" s="32" t="str">
-        <x:v>배포를 누르고 관리용 Google 계정으로 권한을 승인합니다.
-참고  권한 안내가 나오면 항목을 확인한 뒤 허용합니다.</x:v>
-      </x:c>
-      <x:c r="E12" s="109"/>
+      <x:c r="B12" s="175" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="179" t="str">
+        <x:v>공개 저장소 만들기</x:v>
+      </x:c>
+      <x:c r="D12" s="160" t="str">
+        <x:v>https://github.com/school-training-sign/training-sign-template에서 Use this template → Create a new repository를 누릅니다.
+참고  저장소 이름은 training-sign, 공개 범위는 Public으로 설정합니다.</x:v>
+      </x:c>
+      <x:c r="E12" s="161"/>
       <x:c r="F12" s="3"/>
     </x:row>
-    <x:row r="13" ht="43.5" customHeight="1">
+    <x:row r="13" ht="57" customHeight="1">
       <x:c r="A13" s="3"/>
-      <x:c r="B13" s="108" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="31" t="str">
-        <x:v>웹앱 주소 복사</x:v>
-      </x:c>
-      <x:c r="D13" s="32" t="str">
-        <x:v>배포 완료 화면에서 /exec로 끝나는 웹 앱 URL을 복사합니다.
-참고  이 URL은 공개 화면을 Google 시트 백엔드에 연결할 때만 사용합니다.</x:v>
-      </x:c>
-      <x:c r="E13" s="109"/>
+      <x:c r="B13" s="175" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="179" t="str">
+        <x:v>웹앱 주소 연결</x:v>
+      </x:c>
+      <x:c r="D13" s="160" t="str">
+        <x:v>내 저장소의 assets/config.js를 열어 안내된 자리에 복사한 /exec 주소를 넣고 저장합니다.
+참고  초기 설정 코드·비밀번호·공유 키·명단은 GitHub 저장소에 넣지 않습니다.</x:v>
+      </x:c>
+      <x:c r="E13" s="161"/>
       <x:c r="F13" s="3"/>
     </x:row>
-    <x:row r="14" ht="20.25" customHeight="1">
+    <x:row r="14" ht="57" customHeight="1">
       <x:c r="A14" s="3"/>
-      <x:c r="B14" s="104"/>
-      <x:c r="C14" s="3"/>
-      <x:c r="D14" s="3"/>
-      <x:c r="E14" s="105"/>
+      <x:c r="B14" s="175" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C14" s="179" t="str">
+        <x:v>Pages와 관리자 확인</x:v>
+      </x:c>
+      <x:c r="D14" s="160" t="str">
+        <x:v>Settings → Pages에서 Deploy from a branch, main, /(root)를 선택합니다.
+참고  Pages 주소에서 관리자 버튼을 눌렀을 때 첫 설정 화면이 보이면 연결이 끝난 것입니다.</x:v>
+      </x:c>
+      <x:c r="E14" s="161"/>
       <x:c r="F14" s="3"/>
     </x:row>
-    <x:row r="15" ht="24" customHeight="1">
+    <x:row r="15" ht="20.25" customHeight="1">
       <x:c r="A15" s="3"/>
-      <x:c r="B15" s="110" t="str">
-        <x:v>2. GitHub Pages 화면 만들기</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="str">
-        <x:v>2. GitHub Pages 화면 만들기</x:v>
-      </x:c>
-      <x:c r="D15" s="39" t="str">
-        <x:v>2. GitHub Pages 화면 만들기</x:v>
-      </x:c>
-      <x:c r="E15" s="111" t="str">
-        <x:v>2. GitHub Pages 화면 만들기</x:v>
-      </x:c>
+      <x:c r="B15" s="138"/>
+      <x:c r="C15" s="138"/>
+      <x:c r="D15" s="138"/>
+      <x:c r="E15" s="138"/>
       <x:c r="F15" s="3"/>
     </x:row>
-    <x:row r="16" ht="43.5" customHeight="1">
+    <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="3"/>
-      <x:c r="B16" s="112" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="47" t="str">
-        <x:v>배포 템플릿 열기</x:v>
-      </x:c>
-      <x:c r="D16" s="32" t="str">
-        <x:v>아래 템플릿 저장소를 엽니다.
-참고  https://github.com/school-training-sign/training-sign-template</x:v>
-      </x:c>
-      <x:c r="E16" s="109"/>
+      <x:c r="B16" s="188" t="str">
+        <x:v>3. 관리자 첫 설정</x:v>
+      </x:c>
+      <x:c r="C16" s="189"/>
+      <x:c r="D16" s="189"/>
+      <x:c r="E16" s="190"/>
       <x:c r="F16" s="3"/>
     </x:row>
     <x:row r="17" ht="43.5" customHeight="1">
       <x:c r="A17" s="3"/>
-      <x:c r="B17" s="112" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="47" t="str">
-        <x:v>내 저장소 만들기</x:v>
-      </x:c>
-      <x:c r="D17" s="32" t="str">
-        <x:v>Use this template → Create a new repository를 누릅니다.
-참고  저장소 이름은 training-sign, 공개 범위는 Public을 권장합니다.</x:v>
-      </x:c>
-      <x:c r="E17" s="109"/>
+      <x:c r="B17" s="193" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="197" t="str">
+        <x:v>관리자 비밀번호 만들기</x:v>
+      </x:c>
+      <x:c r="D17" s="160" t="str">
+        <x:v>초기 설정 코드와 관리자 비밀번호를 입력합니다.
+참고  숫자 4자리 또는 문자·숫자를 포함한 10자 이상 비밀번호를 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="E17" s="161"/>
       <x:c r="F17" s="3"/>
     </x:row>
     <x:row r="18" ht="43.5" customHeight="1">
       <x:c r="A18" s="3"/>
-      <x:c r="B18" s="112" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="47" t="str">
-        <x:v>백엔드 주소 연결</x:v>
-      </x:c>
-      <x:c r="D18" s="32" t="str">
-        <x:v>내 저장소의 assets/config.js를 열고 안내된 자리에 복사한 /exec 주소를 넣어 저장합니다.
-참고  초기 설정 코드·비밀번호·공유 키·명단은 저장소에 넣지 않습니다.</x:v>
-      </x:c>
-      <x:c r="E18" s="109"/>
+      <x:c r="B18" s="193" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="197" t="str">
+        <x:v>기관 설정 입력</x:v>
+      </x:c>
+      <x:c r="D18" s="160" t="str">
+        <x:v>기관 설정에서 학교명·부제목·안내문·개인정보 처리 안내·대표 색상을 저장합니다.
+참고  개인정보 안내가 비어 있으면 연수를 활성화할 수 없습니다.</x:v>
+      </x:c>
+      <x:c r="E18" s="161"/>
       <x:c r="F18" s="3"/>
     </x:row>
     <x:row r="19" ht="43.5" customHeight="1">
       <x:c r="A19" s="3"/>
-      <x:c r="B19" s="112" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="47" t="str">
-        <x:v>GitHub Pages 켜기</x:v>
-      </x:c>
-      <x:c r="D19" s="32" t="str">
-        <x:v>Settings → Pages에서 Deploy from a branch, main, /(root)를 선택합니다.
-참고  몇 분 뒤 https://사용자명.github.io/training-sign/ 주소가 열립니다.</x:v>
-      </x:c>
-      <x:c r="E19" s="109"/>
-      <x:c r="F19" s="3"/>
-    </x:row>
-    <x:row r="20" ht="43.5" customHeight="1">
-      <x:c r="A20" s="3"/>
-      <x:c r="B20" s="112" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="47" t="str">
-        <x:v>연결 확인</x:v>
-      </x:c>
-      <x:c r="D20" s="32" t="str">
-        <x:v>GitHub Pages 주소에서 관리자 버튼을 누릅니다.
-참고  첫 설정 화면이 보이면 Google 백엔드 연결이 끝난 것입니다.</x:v>
-      </x:c>
-      <x:c r="E20" s="109"/>
-      <x:c r="F20" s="3"/>
-    </x:row>
-    <x:row r="21" ht="20.25" customHeight="1">
-      <x:c r="A21" s="3"/>
-      <x:c r="B21" s="104"/>
-      <x:c r="C21" s="3"/>
-      <x:c r="D21" s="3"/>
-      <x:c r="E21" s="105"/>
-      <x:c r="F21" s="3"/>
-    </x:row>
-    <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="3"/>
-      <x:c r="B22" s="113" t="str">
-        <x:v>3. 관리자 첫 설정</x:v>
-      </x:c>
-      <x:c r="C22" s="54" t="str">
-        <x:v>3. 관리자 첫 설정</x:v>
-      </x:c>
-      <x:c r="D22" s="54" t="str">
-        <x:v>3. 관리자 첫 설정</x:v>
-      </x:c>
-      <x:c r="E22" s="114" t="str">
-        <x:v>3. 관리자 첫 설정</x:v>
-      </x:c>
-      <x:c r="F22" s="3"/>
-    </x:row>
-    <x:row r="23" ht="43.5" customHeight="1">
-      <x:c r="A23" s="3"/>
-      <x:c r="B23" s="115" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="62" t="str">
-        <x:v>관리자 비밀번호 만들기</x:v>
-      </x:c>
-      <x:c r="D23" s="32" t="str">
-        <x:v>초기 설정 코드와 관리자 비밀번호를 입력합니다.
-참고  숫자 4자리 또는 문자·숫자를 포함한 10자 이상 비밀번호를 사용할 수 있습니다.</x:v>
-      </x:c>
-      <x:c r="E23" s="109"/>
-      <x:c r="F23" s="3"/>
-    </x:row>
-    <x:row r="24" ht="43.5" customHeight="1">
-      <x:c r="A24" s="3"/>
-      <x:c r="B24" s="115" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="62" t="str">
-        <x:v>기관 설정 입력</x:v>
-      </x:c>
-      <x:c r="D24" s="32" t="str">
-        <x:v>기관 설정에서 학교명·부제목·안내문·개인정보 처리 안내·대표 색상을 저장합니다.
-참고  개인정보 안내가 비어 있으면 연수를 활성화할 수 없습니다.</x:v>
-      </x:c>
-      <x:c r="E24" s="109"/>
-      <x:c r="F24" s="3"/>
-    </x:row>
-    <x:row r="25" ht="43.5" customHeight="1">
-      <x:c r="A25" s="3"/>
-      <x:c r="B25" s="115" t="str">
+      <x:c r="B19" s="193" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C25" s="62" t="str">
+      <x:c r="C19" s="197" t="str">
         <x:v>구성원 등록</x:v>
       </x:c>
-      <x:c r="D25" s="32" t="str">
+      <x:c r="D19" s="160" t="str">
         <x:v>구성원에서 부서와 성명을 등록합니다.
 참고  이름은 띄어쓰기·쉼표·줄바꿈으로 여러 명을 한 번에 입력하거나 엑셀·CSV를 가져올 수 있습니다.</x:v>
       </x:c>
-      <x:c r="E25" s="109"/>
-      <x:c r="F25" s="3"/>
-    </x:row>
-    <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="3"/>
-      <x:c r="B26" s="115" t="str">
+      <x:c r="E19" s="161"/>
+      <x:c r="F19" s="3"/>
+    </x:row>
+    <x:row r="20" ht="57" customHeight="1">
+      <x:c r="A20" s="3"/>
+      <x:c r="B20" s="193" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C26" s="62" t="str">
+      <x:c r="C20" s="197" t="str">
         <x:v>연수 등록</x:v>
       </x:c>
-      <x:c r="D26" s="32" t="str">
+      <x:c r="D20" s="160" t="str">
         <x:v>연수에서 날짜·시간·활성 상태와 서명 대상(전체 구성원 또는 부서 선택)을 정합니다.
 참고  필요한 연수에만 현장 접수 코드 사용을 켭니다. 기존 연수와 이 항목을 끈 연수는 코드 없이 운영됩니다.</x:v>
       </x:c>
-      <x:c r="E26" s="109"/>
-      <x:c r="F26" s="3"/>
-    </x:row>
-    <x:row r="27" ht="43.5" customHeight="1">
-      <x:c r="A27" s="3"/>
-      <x:c r="B27" s="115" t="str">
+      <x:c r="E20" s="161"/>
+      <x:c r="F20" s="3"/>
+    </x:row>
+    <x:row r="21" ht="43.5" customHeight="1">
+      <x:c r="A21" s="3"/>
+      <x:c r="B21" s="193" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C27" s="62" t="str">
+      <x:c r="C21" s="197" t="str">
         <x:v>공유 링크 배포</x:v>
       </x:c>
-      <x:c r="D27" s="32" t="str">
+      <x:c r="D21" s="160" t="str">
         <x:v>공유·보안에서 참여 링크와 QR을 복사해 학교 내부에 안내합니다.
 참고  링크를 받은 사람은 별도 Google 계정 없이 접속합니다.</x:v>
       </x:c>
-      <x:c r="E27" s="109"/>
-      <x:c r="F27" s="3"/>
-    </x:row>
-    <x:row r="28" ht="20.25" customHeight="1">
-      <x:c r="A28" s="3"/>
-      <x:c r="B28" s="104"/>
-      <x:c r="C28" s="3"/>
-      <x:c r="D28" s="3"/>
-      <x:c r="E28" s="105"/>
-      <x:c r="F28" s="3"/>
-    </x:row>
-    <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="3"/>
-      <x:c r="B29" s="106" t="str">
+      <x:c r="E21" s="161"/>
+      <x:c r="F21" s="3"/>
+    </x:row>
+    <x:row r="22" ht="20.25" customHeight="1">
+      <x:c r="A22" s="3"/>
+      <x:c r="B22" s="138"/>
+      <x:c r="C22" s="138"/>
+      <x:c r="D22" s="138"/>
+      <x:c r="E22" s="138"/>
+      <x:c r="F22" s="3"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="3"/>
+      <x:c r="B23" s="147" t="str">
         <x:v>4. 연수 운영과 출력</x:v>
       </x:c>
-      <x:c r="C29" s="23" t="str">
-        <x:v>4. 연수 운영과 출력</x:v>
-      </x:c>
-      <x:c r="D29" s="23" t="str">
-        <x:v>4. 연수 운영과 출력</x:v>
-      </x:c>
-      <x:c r="E29" s="107" t="str">
-        <x:v>4. 연수 운영과 출력</x:v>
-      </x:c>
-      <x:c r="F29" s="3"/>
-    </x:row>
-    <x:row r="30" ht="43.5" customHeight="1">
-      <x:c r="A30" s="3"/>
-      <x:c r="B30" s="108" t="str">
+      <x:c r="C23" s="148"/>
+      <x:c r="D23" s="148"/>
+      <x:c r="E23" s="149"/>
+      <x:c r="F23" s="3"/>
+    </x:row>
+    <x:row r="24" ht="57" customHeight="1">
+      <x:c r="A24" s="3"/>
+      <x:c r="B24" s="152" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C30" s="66" t="str">
+      <x:c r="C24" s="201" t="str">
         <x:v>현장 접수와 참여</x:v>
       </x:c>
-      <x:c r="D30" s="32" t="str">
+      <x:c r="D24" s="160" t="str">
         <x:v>현장 코드 연수는 카드에서 5·10·15분 접수를 열고 화면의 6자리 코드를 현장에서 안내합니다.
 참고  재발급·종료 시 이전 코드는 즉시 무효화되며, 오늘·매일 연수는 등록된 종료 시각에 맞춰 접수도 끝납니다.</x:v>
       </x:c>
-      <x:c r="E30" s="109"/>
+      <x:c r="E24" s="161"/>
+      <x:c r="F24" s="3"/>
+    </x:row>
+    <x:row r="25" ht="57" customHeight="1">
+      <x:c r="A25" s="3"/>
+      <x:c r="B25" s="152" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C25" s="201" t="str">
+        <x:v>미서명 현황 확인</x:v>
+      </x:c>
+      <x:c r="D25" s="160" t="str">
+        <x:v>연수 목록에서 미서명 현황을 눌러 미서명만 또는 전체 현황을 확인합니다.
+참고  매일 연수는 날짜를 바꿀 수 있으며 대상·서명·미서명·서명률과 서명 시각을 볼 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="E25" s="161"/>
+      <x:c r="F25" s="3"/>
+    </x:row>
+    <x:row r="26" ht="43.5" customHeight="1">
+      <x:c r="A26" s="3"/>
+      <x:c r="B26" s="152" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C26" s="201" t="str">
+        <x:v>서명 기록 확인</x:v>
+      </x:c>
+      <x:c r="D26" s="160" t="str">
+        <x:v>서명 기록에서 연수를 선택하면 해당 연수 날짜가 자동으로 설정됩니다.
+참고  잘못 제출된 기록은 개별 삭제할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="E26" s="161"/>
+      <x:c r="F26" s="3"/>
+    </x:row>
+    <x:row r="27" ht="57" customHeight="1">
+      <x:c r="A27" s="3"/>
+      <x:c r="B27" s="152" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="201" t="str">
+        <x:v>출력 미리보기</x:v>
+      </x:c>
+      <x:c r="D27" s="160" t="str">
+        <x:v>연수 목록의 출력 버튼에서 날짜·열 수·정렬·서명률·PDF·엑셀·인쇄를 고릅니다.
+참고  실제 서명 이미지가 들어간 A4 미리보기를 먼저 확인하며 단계별 진행 상태가 표시됩니다.</x:v>
+      </x:c>
+      <x:c r="E27" s="161"/>
+      <x:c r="F27" s="3"/>
+    </x:row>
+    <x:row r="28" ht="43.5" customHeight="1">
+      <x:c r="A28" s="3"/>
+      <x:c r="B28" s="152" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C28" s="201" t="str">
+        <x:v>파일 보관</x:v>
+      </x:c>
+      <x:c r="D28" s="160" t="str">
+        <x:v>PDF 또는 엑셀을 내려받아 학교가 정한 보관 위치에 저장합니다.
+참고  인쇄하기만 실행한 작업은 원본 삭제 조건을 충족하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="E28" s="161"/>
+      <x:c r="F28" s="3"/>
+    </x:row>
+    <x:row r="29" ht="43.5" customHeight="1">
+      <x:c r="A29" s="3"/>
+      <x:c r="B29" s="152" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C29" s="201" t="str">
+        <x:v>원본 삭제</x:v>
+      </x:c>
+      <x:c r="D29" s="160" t="str">
+        <x:v>보관 파일을 확인한 뒤 연수명을 다시 입력해 해당 날짜의 원본 서명과 PNG를 삭제합니다.
+참고  출력 파일은 비공개 Drive의 출력 보관 폴더에 남습니다.</x:v>
+      </x:c>
+      <x:c r="E29" s="161"/>
+      <x:c r="F29" s="3"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="3"/>
+      <x:c r="B30" s="210" t="str">
+        <x:v>5. 보안·복구</x:v>
+      </x:c>
+      <x:c r="C30" s="211"/>
+      <x:c r="D30" s="211"/>
+      <x:c r="E30" s="212"/>
       <x:c r="F30" s="3"/>
     </x:row>
     <x:row r="31" ht="43.5" customHeight="1">
       <x:c r="A31" s="3"/>
-      <x:c r="B31" s="108" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C31" s="66" t="str">
-        <x:v>서명 기록 확인</x:v>
-      </x:c>
-      <x:c r="D31" s="32" t="str">
-        <x:v>서명 기록에서 연수를 선택하면 해당 연수 날짜가 자동으로 설정됩니다.
-참고  잘못 제출된 기록은 개별 삭제할 수 있습니다.</x:v>
-      </x:c>
-      <x:c r="E31" s="109"/>
+      <x:c r="B31" s="215" t="str">
+        <x:v>•</x:v>
+      </x:c>
+      <x:c r="C31" s="219" t="str">
+        <x:v>공유 링크 보호</x:v>
+      </x:c>
+      <x:c r="D31" s="160" t="str">
+        <x:v>공유 링크에는 본인 인증이 없습니다. 학교 내부에서만 안내하세요.
+참고  유출되면 공유·보안 → 공유 키 교체 후 새 링크와 QR을 배포합니다.</x:v>
+      </x:c>
+      <x:c r="E31" s="161"/>
       <x:c r="F31" s="3"/>
     </x:row>
     <x:row r="32" ht="43.5" customHeight="1">
       <x:c r="A32" s="3"/>
-      <x:c r="B32" s="108" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C32" s="66" t="str">
-        <x:v>미서명 현황 확인</x:v>
-      </x:c>
-      <x:c r="D32" s="32" t="str">
-        <x:v>연수 목록의 미서명 현황에서 해당 날짜의 미서명자를 확인합니다.
-참고  전체 현황으로 전환하면 서명 여부·완료 시각·서명률을 함께 볼 수 있습니다.</x:v>
-      </x:c>
-      <x:c r="E32" s="109"/>
+      <x:c r="B32" s="215" t="str">
+        <x:v>•</x:v>
+      </x:c>
+      <x:c r="C32" s="219" t="str">
+        <x:v>비밀번호 분실</x:v>
+      </x:c>
+      <x:c r="D32" s="160" t="str">
+        <x:v>학교용 시트에서 🖊️ 전자서명 관리 → 관리자 비밀번호 복구를 누릅니다.
+참고  기존 관리자 세션은 모두 무효화됩니다.</x:v>
+      </x:c>
+      <x:c r="E32" s="161"/>
       <x:c r="F32" s="3"/>
     </x:row>
     <x:row r="33" ht="43.5" customHeight="1">
       <x:c r="A33" s="3"/>
-      <x:c r="B33" s="108" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C33" s="66" t="str">
-        <x:v>출력 미리보기</x:v>
-      </x:c>
-      <x:c r="D33" s="32" t="str">
-        <x:v>연수 목록의 출력 버튼에서 날짜·열 수·정렬·서명률·PDF·엑셀·인쇄를 고릅니다.
-참고  실제 서명 이미지가 들어간 A4 미리보기를 먼저 확인하며 단계별 진행 상태가 표시됩니다.</x:v>
-      </x:c>
-      <x:c r="E33" s="109"/>
+      <x:c r="B33" s="215" t="str">
+        <x:v>•</x:v>
+      </x:c>
+      <x:c r="C33" s="219" t="str">
+        <x:v>데이터 탭 점검</x:v>
+      </x:c>
+      <x:c r="D33" s="160" t="str">
+        <x:v>🖊️ 전자서명 관리 → 데이터 탭 표시·숨기기를 사용합니다.
+참고  관리용 Google 계정 외에는 시트 편집 권한을 주지 않습니다.</x:v>
+      </x:c>
+      <x:c r="E33" s="161"/>
       <x:c r="F33" s="3"/>
     </x:row>
-    <x:row r="34" ht="43.5" customHeight="1">
+    <x:row r="34" ht="57" customHeight="1">
       <x:c r="A34" s="3"/>
-      <x:c r="B34" s="108" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C34" s="66" t="str">
-        <x:v>파일 보관</x:v>
-      </x:c>
-      <x:c r="D34" s="32" t="str">
-        <x:v>PDF 또는 엑셀을 내려받아 학교가 정한 보관 위치에 저장합니다.
-참고  인쇄하기만 실행한 작업은 원본 삭제 조건을 충족하지 않습니다.</x:v>
-      </x:c>
-      <x:c r="E34" s="109"/>
+      <x:c r="B34" s="215" t="str">
+        <x:v>•</x:v>
+      </x:c>
+      <x:c r="C34" s="219" t="str">
+        <x:v>자료 최소 보관</x:v>
+      </x:c>
+      <x:c r="D34" s="160" t="str">
+        <x:v>학교가 정한 보관기간이 끝나면 출력 파일도 관리용 Drive에서 삭제합니다.
+참고  이 시스템은 연수 참여 확인용이며 공식 동의·결재·법적 전자서명용이 아닙니다.</x:v>
+      </x:c>
+      <x:c r="E34" s="161"/>
       <x:c r="F34" s="3"/>
     </x:row>
-    <x:row r="35" ht="43.5" customHeight="1">
+    <x:row r="35" ht="20.25" customHeight="1">
       <x:c r="A35" s="3"/>
-      <x:c r="B35" s="127" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C35" s="131" t="str">
-        <x:v>원본 삭제</x:v>
-      </x:c>
-      <x:c r="D35" s="135" t="str">
-        <x:v>보관 파일을 확인한 뒤 연수명을 다시 입력해 해당 날짜의 원본 서명과 PNG를 삭제합니다.
-참고  출력 파일은 비공개 Drive의 출력 보관 폴더에 남습니다.</x:v>
-      </x:c>
-      <x:c r="E35" s="105"/>
+      <x:c r="B35" s="138"/>
+      <x:c r="C35" s="138"/>
+      <x:c r="D35" s="138"/>
+      <x:c r="E35" s="138"/>
       <x:c r="F35" s="3"/>
     </x:row>
-    <x:row r="36" ht="24" customHeight="1">
+    <x:row r="36" ht="20.25" customHeight="1">
       <x:c r="A36" s="3"/>
-      <x:c r="B36" s="116" t="str">
-        <x:v>5. 보안·복구</x:v>
-      </x:c>
-      <x:c r="C36" s="73" t="str">
-        <x:v>5. 보안·복구</x:v>
-      </x:c>
-      <x:c r="D36" s="73" t="str">
-        <x:v>5. 보안·복구</x:v>
-      </x:c>
-      <x:c r="E36" s="117" t="str">
-        <x:v>5. 보안·복구</x:v>
-      </x:c>
+      <x:c r="B36" s="222" t="str">
+        <x:v>공식 참고 문서</x:v>
+      </x:c>
+      <x:c r="C36" s="223"/>
+      <x:c r="D36" s="223"/>
+      <x:c r="E36" s="224"/>
       <x:c r="F36" s="3"/>
     </x:row>
-    <x:row r="37" ht="43.5" customHeight="1">
+    <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="3"/>
-      <x:c r="B37" s="118" t="str">
-        <x:v>•</x:v>
-      </x:c>
-      <x:c r="C37" s="81" t="str">
-        <x:v>공유 링크 보호</x:v>
-      </x:c>
-      <x:c r="D37" s="32" t="str">
-        <x:v>공유 링크에는 본인 인증이 없습니다. 학교 내부에서만 안내하세요.
-참고  유출되면 공유·보안 → 공유 키 교체 후 새 링크와 QR을 배포합니다.</x:v>
-      </x:c>
-      <x:c r="E37" s="109"/>
+      <x:c r="B37" s="232" t="str">
+        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
+Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
+      </x:c>
+      <x:c r="C37" s="233"/>
+      <x:c r="D37" s="233"/>
+      <x:c r="E37" s="234"/>
       <x:c r="F37" s="3"/>
     </x:row>
-    <x:row r="38" ht="43.5" customHeight="1">
+    <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="3"/>
-      <x:c r="B38" s="118" t="str">
-        <x:v>•</x:v>
-      </x:c>
-      <x:c r="C38" s="81" t="str">
-        <x:v>비밀번호 분실</x:v>
-      </x:c>
-      <x:c r="D38" s="32" t="str">
-        <x:v>학교용 시트에서 🖊️ 전자서명 관리 → 관리자 비밀번호 복구를 누릅니다.
-참고  기존 관리자 세션은 모두 무효화됩니다.</x:v>
-      </x:c>
-      <x:c r="E38" s="109"/>
+      <x:c r="B38" s="235"/>
+      <x:c r="C38" s="236"/>
+      <x:c r="D38" s="236"/>
+      <x:c r="E38" s="237"/>
       <x:c r="F38" s="3"/>
     </x:row>
     <x:row r="39" ht="43.5" customHeight="1">
       <x:c r="A39" s="3"/>
-      <x:c r="B39" s="118" t="str">
-        <x:v>•</x:v>
-      </x:c>
-      <x:c r="C39" s="81" t="str">
-        <x:v>데이터 탭 점검</x:v>
-      </x:c>
-      <x:c r="D39" s="32" t="str">
-        <x:v>🖊️ 전자서명 관리 → 데이터 탭 표시·숨기기를 사용합니다.
-참고  관리용 Google 계정 외에는 시트 편집 권한을 주지 않습니다.</x:v>
-      </x:c>
-      <x:c r="E39" s="109"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
       <x:c r="F39" s="3"/>
     </x:row>
     <x:row r="40" ht="43.5" customHeight="1">
       <x:c r="A40" s="3"/>
-      <x:c r="B40" s="118" t="str">
-        <x:v>•</x:v>
-      </x:c>
-      <x:c r="C40" s="81" t="str">
-        <x:v>자료 최소 보관</x:v>
-      </x:c>
-      <x:c r="D40" s="32" t="str">
-        <x:v>학교가 정한 보관기간이 끝나면 출력 파일도 관리용 Drive에서 삭제합니다.
-참고  이 시스템은 연수 참여 확인용이며 공식 동의·결재·법적 전자서명용이 아닙니다.</x:v>
-      </x:c>
-      <x:c r="E40" s="109"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
       <x:c r="F40" s="3"/>
     </x:row>
     <x:row r="41" ht="20.25" customHeight="1">
       <x:c r="A41" s="3"/>
-      <x:c r="B41" s="104"/>
-      <x:c r="C41" s="3"/>
-      <x:c r="D41" s="3"/>
-      <x:c r="E41" s="105"/>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
       <x:c r="F41" s="3"/>
     </x:row>
     <x:row r="42" ht="20.25" customHeight="1">
       <x:c r="A42" s="3"/>
-      <x:c r="B42" s="119" t="str">
-        <x:v>공식 참고 문서</x:v>
-      </x:c>
-      <x:c r="C42" s="83" t="str">
-        <x:v>공식 참고 문서</x:v>
-      </x:c>
-      <x:c r="D42" s="83" t="str">
-        <x:v>공식 참고 문서</x:v>
-      </x:c>
-      <x:c r="E42" s="120" t="str">
-        <x:v>공식 참고 문서</x:v>
-      </x:c>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
       <x:c r="F42" s="3"/>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
       <x:c r="A43" s="3"/>
-      <x:c r="B43" s="92" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="C43" s="93" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="D43" s="93" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="E43" s="94" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
       <x:c r="F43" s="3"/>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
       <x:c r="A44" s="3"/>
-      <x:c r="B44" s="121" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="C44" s="122" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="D44" s="122" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
-      <x:c r="E44" s="123" t="str">
-        <x:v>Google Apps Script 연결형 스크립트  https://developers.google.com/apps-script/guides/bound
-Google Apps Script 웹앱 배포  https://developers.google.com/apps-script/guides/web</x:v>
-      </x:c>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
       <x:c r="F44" s="3"/>
     </x:row>
     <x:row r="45" ht="20.25" customHeight="1">
@@ -1943,39 +2228,34 @@
     <x:mergeCell ref="B2:E2"/>
     <x:mergeCell ref="B3:E3"/>
     <x:mergeCell ref="B4:E4"/>
-    <x:mergeCell ref="B6:E6"/>
     <x:mergeCell ref="D7:E7"/>
     <x:mergeCell ref="D8:E8"/>
     <x:mergeCell ref="D9:E9"/>
-    <x:mergeCell ref="D10:E10"/>
-    <x:mergeCell ref="D11:E11"/>
     <x:mergeCell ref="D12:E12"/>
     <x:mergeCell ref="D13:E13"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="D16:E16"/>
+    <x:mergeCell ref="D14:E14"/>
     <x:mergeCell ref="D17:E17"/>
     <x:mergeCell ref="D18:E18"/>
     <x:mergeCell ref="D19:E19"/>
     <x:mergeCell ref="D20:E20"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="D23:E23"/>
+    <x:mergeCell ref="D21:E21"/>
     <x:mergeCell ref="D24:E24"/>
     <x:mergeCell ref="D25:E25"/>
     <x:mergeCell ref="D26:E26"/>
     <x:mergeCell ref="D27:E27"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="D30:E30"/>
+    <x:mergeCell ref="D28:E28"/>
+    <x:mergeCell ref="D29:E29"/>
     <x:mergeCell ref="D31:E31"/>
     <x:mergeCell ref="D32:E32"/>
     <x:mergeCell ref="D33:E33"/>
     <x:mergeCell ref="D34:E34"/>
+    <x:mergeCell ref="B6:E6"/>
+    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="D37:E37"/>
-    <x:mergeCell ref="D38:E38"/>
-    <x:mergeCell ref="D39:E39"/>
-    <x:mergeCell ref="D40:E40"/>
-    <x:mergeCell ref="B42:E42"/>
-    <x:mergeCell ref="B43:E44"/>
+    <x:mergeCell ref="B37:E38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R55ad3386aa4c4ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R5514eb3040864bbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,11 +571,11 @@
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>새 사본에서 🖊️ 전자서명 관리 → 초기 설정 실행을 누르고, 완료 창의 초기 설정 코드를 보관합니다.
-참고  ‘Google에서 확인하지 않은 앱’이 나오면 개발자 이메일이 본인 계정인지 확인한 뒤 고급 → 학교 연수 전자서명 시스템으로 이동 → 허용을 누릅니다. 모르는 이메일이거나 Google Workspace 정책이 차단하면 중단하고 관리자에게 문의하세요. 소유자만 처음 한 번 승인하며 서명 참여자에게는 이 화면이 나타나지 않습니다.</x:v>
+참고  ‘Google에서 확인하지 않은 앱’이 나오면 이 사본을 만든 본인 Google 계정으로 로그인했는지 확인한 뒤 고급 → 학교 연수 전자서명 시스템으로 이동 → 허용을 누릅니다. 본인이 만들지 않은 사본이거나 Google Workspace 정책이 차단하면 중단하고 관리자에게 문의하세요. 사본 소유자만 처음 한 번 승인하며 서명 참여자에게는 이 화면이 나타나지 않습니다.</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
         <x:v>새 사본에서 🖊️ 전자서명 관리 → 초기 설정 실행을 누르고, 완료 창의 초기 설정 코드를 보관합니다.
-참고  ‘Google에서 확인하지 않은 앱’이 나오면 개발자 이메일이 본인 계정인지 확인한 뒤 고급 → 학교 연수 전자서명 시스템으로 이동 → 허용을 누릅니다. 모르는 이메일이거나 Google Workspace 정책이 차단하면 중단하고 관리자에게 문의하세요. 소유자만 처음 한 번 승인하며 서명 참여자에게는 이 화면이 나타나지 않습니다.</x:v>
+참고  ‘Google에서 확인하지 않은 앱’이 나오면 이 사본을 만든 본인 Google 계정으로 로그인했는지 확인한 뒤 고급 → 학교 연수 전자서명 시스템으로 이동 → 허용을 누릅니다. 본인이 만들지 않은 사본이거나 Google Workspace 정책이 차단하면 중단하고 관리자에게 문의하세요. 사본 소유자만 처음 한 번 승인하며 서명 참여자에게는 이 화면이 나타나지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
